--- a/output/pdf_financials_xlsx/MPC.xlsx
+++ b/output/pdf_financials_xlsx/MPC.xlsx
@@ -3389,46 +3389,46 @@
         <v>0.696</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>31.852</v>
+        <v>1.952</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.569</v>
+        <v>6.558</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.026</v>
+        <v>3.065</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.112</v>
+        <v>4.218</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>2.359</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>3.193</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>4.699</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0</v>
+        <v>3.157</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>3.519</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.11</v>
+        <v>3.849</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0</v>
+        <v>3.733</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>6.352</v>
+        <v>4.777</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>6.441</v>
+        <v>5.419</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.901</v>
+        <v>2.075</v>
       </c>
     </row>
     <row r="49">
@@ -3454,34 +3454,48 @@
         <v>32.406</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>6.558</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>3.065</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>4.218</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>3.193</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>4.699</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>3.157</v>
-      </c>
-      <c r="M49" s="3" t="n">
-        <v>3.519</v>
+        <v>10.547</v>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N49" s="3" t="n">
         <v>46.364</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>3.733</v>
+        <v>45.954</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>51.509</v>
@@ -4292,26 +4306,40 @@
       <c r="F62" s="3" t="n">
         <v>322.034</v>
       </c>
-      <c r="G62" s="3" t="n">
-        <v>391.998</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>430.471</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>478.18</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>514.926</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>569.968</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>625.973</v>
-      </c>
-      <c r="M62" s="3" t="n">
-        <v>694</v>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N62" s="3" t="n">
         <v>694.975</v>
@@ -9578,7 +9606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -12087,7 +12115,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14222,7 +14250,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -16266,7 +16294,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -17353,7 +17381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">

--- a/output/pdf_financials_xlsx/MPC.xlsx
+++ b/output/pdf_financials_xlsx/MPC.xlsx
@@ -1137,49 +1137,49 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.117</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.165</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.201</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.662</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>1.287</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.511</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="13">
@@ -2099,49 +2099,49 @@
         <v>5.557</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>16.086</v>
+        <v>15.42</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>17.872</v>
+        <v>17.801</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14.729</v>
+        <v>14.339</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>20.597</v>
+        <v>19.647</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>36.616</v>
+        <v>35.676</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>64.804</v>
+        <v>63.687</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>62.275</v>
+        <v>62.11</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>52.642</v>
+        <v>52.164</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>42.219</v>
+        <v>41.018</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>36.304</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>61.871</v>
+        <v>61.408</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>78.19499999999999</v>
+        <v>77.533</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>24.246</v>
+        <v>22.959</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.933</v>
+        <v>-5.444</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>6.357</v>
+        <v>6.206</v>
       </c>
     </row>
     <row r="28">
@@ -2215,49 +2215,49 @@
         <v>7.973</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>16.086</v>
+        <v>15.42</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>17.872</v>
+        <v>17.801</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>14.729</v>
+        <v>14.339</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>20.597</v>
+        <v>19.647</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>36.616</v>
+        <v>35.676</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>64.804</v>
+        <v>63.687</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>62.275</v>
+        <v>62.11</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>52.642</v>
+        <v>52.164</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>42.219</v>
+        <v>41.018</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>36.304</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>61.871</v>
+        <v>61.408</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>78.19499999999999</v>
+        <v>77.533</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>24.246</v>
+        <v>22.959</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.933</v>
+        <v>-5.444</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>6.357</v>
+        <v>6.206</v>
       </c>
     </row>
     <row r="30">
@@ -2515,15 +2515,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>25.446</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>17.835</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.915</v>
@@ -2639,15 +2635,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>25.446</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>17.835</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.915</v>
@@ -3389,46 +3381,46 @@
         <v>0.696</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.952</v>
+        <v>31.852</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.558</v>
+        <v>2.569</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.065</v>
+        <v>2.026</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>4.218</v>
+        <v>0.112</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.359</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.193</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.699</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.157</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.519</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.849</v>
+        <v>4.11</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>3.733</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>4.777</v>
+        <v>6.352</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.419</v>
+        <v>6.441</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.075</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="49">
@@ -3454,48 +3446,34 @@
         <v>32.406</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>10.547</v>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.558</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>3.065</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>4.218</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>3.193</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>4.699</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>3.519</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>46.364</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>45.954</v>
+        <v>3.733</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>51.509</v>
@@ -4306,40 +4284,26 @@
       <c r="F62" s="3" t="n">
         <v>322.034</v>
       </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="3" t="n">
+        <v>391.998</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>430.471</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>478.18</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>514.926</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>569.968</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>625.973</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>694</v>
       </c>
       <c r="N62" s="3" t="n">
         <v>694.975</v>
@@ -9606,7 +9570,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -12115,7 +12079,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14250,7 +14214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -16294,7 +16258,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -17381,7 +17345,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -18776,7 +18740,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -51060,7 +51024,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -51163,7 +51127,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -52664,7 +52628,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -52765,7 +52729,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -54228,7 +54192,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -54327,7 +54291,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -55177,7 +55141,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -57267,7 +57231,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -59082,7 +59046,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -59183,7 +59147,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">

--- a/output/pdf_financials_xlsx/MPC.xlsx
+++ b/output/pdf_financials_xlsx/MPC.xlsx
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>31.331</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -4400,46 +4400,46 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.872</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>2.481</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.056</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.569</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.745</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.671</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>4.061</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>4.484</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
@@ -7740,15 +7740,11 @@
       <c r="O119" s="3" t="n">
         <v>-32.143</v>
       </c>
-      <c r="P119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P119" s="3" t="n">
+        <v>11.268</v>
+      </c>
+      <c r="Q119" s="3" t="n">
+        <v>3.624</v>
       </c>
       <c r="R119" s="1" t="inlineStr">
         <is>
@@ -8718,20 +8714,14 @@
       <c r="O135" s="3" t="n">
         <v>10.886</v>
       </c>
-      <c r="P135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P135" s="3" t="n">
+        <v>5.837</v>
+      </c>
+      <c r="Q135" s="3" t="n">
+        <v>-20.322</v>
+      </c>
+      <c r="R135" s="3" t="n">
+        <v>5.67</v>
       </c>
     </row>
   </sheetData>
@@ -21041,7 +21031,11 @@
           <t>Net income (loss) 31,651</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -22542,7 +22536,11 @@
           <t>Cash generated from (used in) operating activities 11,097</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -24344,7 +24342,11 @@
           <t>Net income (loss) 5,069</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -25871,7 +25873,11 @@
           <t>Cash generated from (used in) operating activities 5,670</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -32681,7 +32687,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -48319,7 +48329,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E402" s="5" t="n">
         <v>-1.781</v>
       </c>
@@ -62224,7 +62238,11 @@
           <t>Net income from discontinued operations (note 19)</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr"/>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E545" s="5" t="n">
         <v>31.331</v>
       </c>
